--- a/sources/countries.xlsx
+++ b/sources/countries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\xqsme\workspace\bootdotdev\geography_quiz\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1B9E8C-AFB1-4B97-A84C-866575B90363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65337B0D-E7D2-4DEE-9637-7FB931D83957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{89D391DB-B8B7-4455-8CF3-B5826679EB4E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{89D391DB-B8B7-4455-8CF3-B5826679EB4E}"/>
   </bookViews>
   <sheets>
     <sheet name="countries" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="1458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="1456">
   <si>
     <t>name</t>
   </si>
@@ -2870,9 +2870,6 @@
     <t>SG</t>
   </si>
   <si>
-    <t>Singapur</t>
-  </si>
-  <si>
     <t>Singaporean</t>
   </si>
   <si>
@@ -3744,9 +3741,6 @@
   </si>
   <si>
     <t>São Toméan</t>
-  </si>
-  <si>
-    <t>City of San Marino</t>
   </si>
   <si>
     <t>the Solomons</t>
@@ -5318,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C1" t="s">
         <v>1190</v>
       </c>
-      <c r="C1" t="s">
-        <v>1191</v>
-      </c>
       <c r="D1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -5333,7 +5327,7 @@
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="H1" t="s">
         <v>3</v>
@@ -5345,7 +5339,7 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="L1" t="s">
         <v>4</v>
@@ -5368,7 +5362,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5408,13 +5402,13 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
@@ -5436,7 +5430,7 @@
         <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="L3">
         <v>30654</v>
@@ -5456,7 +5450,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -5502,7 +5496,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -5589,7 +5583,7 @@
         <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -5600,7 +5594,7 @@
         <v>45</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>46</v>
@@ -5635,7 +5629,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -5690,7 +5684,7 @@
         <v>56</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>57</v>
@@ -5731,7 +5725,7 @@
         <v>63</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="H10" s="1" t="e">
         <f>NA()</f>
@@ -5774,7 +5768,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>69</v>
@@ -5811,7 +5805,7 @@
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>72</v>
@@ -5855,7 +5849,7 @@
         <v>77</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -5901,7 +5895,7 @@
         <v>83</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -5912,7 +5906,7 @@
         <v>85</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>86</v>
@@ -5947,7 +5941,7 @@
         <v>88</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -5993,7 +5987,7 @@
         <v>94</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -6039,7 +6033,7 @@
         <v>100</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -6050,7 +6044,7 @@
         <v>102</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>103</v>
@@ -6073,24 +6067,24 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>1045</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>1046</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>194</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>58</v>
@@ -6099,7 +6093,7 @@
         <v>59</v>
       </c>
       <c r="K18" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="L18">
         <v>398165</v>
@@ -6119,7 +6113,7 @@
         <v>105</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -6165,7 +6159,7 @@
         <v>110</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -6255,7 +6249,7 @@
         <v>120</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -6301,7 +6295,7 @@
         <v>126</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -6391,7 +6385,7 @@
         <v>137</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -6463,7 +6457,7 @@
         <v>149</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -6509,7 +6503,7 @@
         <v>154</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -6552,21 +6546,21 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>1187</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="H29" s="1" t="e">
         <f>NA()</f>
@@ -6602,7 +6596,7 @@
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>160</v>
@@ -6611,7 +6605,7 @@
         <v>161</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>162</v>
@@ -6646,7 +6640,7 @@
         <v>164</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -6657,7 +6651,7 @@
         <v>166</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>167</v>
@@ -6669,7 +6663,7 @@
         <v>168</v>
       </c>
       <c r="K31" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="L31">
         <v>2359609</v>
@@ -6727,7 +6721,7 @@
         <v>172</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -6741,7 +6735,7 @@
         <v>174</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>58</v>
@@ -6773,7 +6767,7 @@
         <v>176</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -6814,26 +6808,26 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>1157</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>1158</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>58</v>
@@ -6842,7 +6836,7 @@
         <v>59</v>
       </c>
       <c r="K35" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="L35">
         <v>39471</v>
@@ -6863,7 +6857,7 @@
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
@@ -6873,7 +6867,7 @@
         <v>183</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>184</v>
@@ -6908,7 +6902,7 @@
         <v>187</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -6919,7 +6913,7 @@
         <v>189</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>190</v>
@@ -6963,7 +6957,7 @@
         <v>194</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>195</v>
@@ -6975,7 +6969,7 @@
         <v>141</v>
       </c>
       <c r="K38" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="L38">
         <v>24070553</v>
@@ -6998,7 +6992,7 @@
         <v>196</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -7041,10 +7035,10 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
@@ -7069,7 +7063,7 @@
         <v>141</v>
       </c>
       <c r="K40" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="L40">
         <v>491233</v>
@@ -7092,7 +7086,7 @@
         <v>201</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -7103,7 +7097,7 @@
         <v>203</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>204</v>
@@ -7138,7 +7132,7 @@
         <v>206</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -7152,7 +7146,7 @@
         <v>208</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>33</v>
@@ -7228,7 +7222,7 @@
         <v>219</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -7239,7 +7233,7 @@
         <v>221</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>222</v>
@@ -7271,7 +7265,7 @@
         <v>224</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -7282,7 +7276,7 @@
         <v>226</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>227</v>
@@ -7317,7 +7311,7 @@
         <v>229</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -7363,7 +7357,7 @@
         <v>234</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -7409,7 +7403,7 @@
         <v>239</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -7420,7 +7414,7 @@
         <v>241</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>242</v>
@@ -7455,7 +7449,7 @@
         <v>245</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -7466,7 +7460,7 @@
         <v>247</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>248</v>
@@ -7478,7 +7472,7 @@
         <v>92</v>
       </c>
       <c r="K49" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="L49">
         <v>1692</v>
@@ -7498,11 +7492,11 @@
         <v>249</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>250</v>
@@ -7523,7 +7517,7 @@
         <v>92</v>
       </c>
       <c r="K50" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="L50">
         <v>593</v>
@@ -7543,7 +7537,7 @@
         <v>253</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -7589,7 +7583,7 @@
         <v>258</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -7612,7 +7606,7 @@
         <v>180</v>
       </c>
       <c r="K52" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="L52">
         <v>944388</v>
@@ -7626,11 +7620,11 @@
         <v>262</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>263</v>
@@ -7674,7 +7668,7 @@
         <v>267</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -7697,7 +7691,7 @@
         <v>41</v>
       </c>
       <c r="K54" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="L54">
         <v>15040</v>
@@ -7717,7 +7711,7 @@
         <v>271</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -7728,10 +7722,10 @@
         <v>273</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>58</v>
@@ -7763,7 +7757,7 @@
         <v>275</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -7809,7 +7803,7 @@
         <v>280</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -7852,7 +7846,7 @@
         <v>285</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -7863,7 +7857,7 @@
         <v>287</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>288</v>
@@ -7875,7 +7869,7 @@
         <v>59</v>
       </c>
       <c r="K58" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="L58">
         <v>156115</v>
@@ -7895,7 +7889,7 @@
         <v>289</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -7941,11 +7935,11 @@
         <v>294</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>295</v>
@@ -7954,7 +7948,7 @@
         <v>296</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>297</v>
@@ -7989,11 +7983,11 @@
         <v>299</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>300</v>
@@ -8046,7 +8040,7 @@
         <v>305</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>306</v>
@@ -8081,7 +8075,7 @@
         <v>308</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -8095,7 +8089,7 @@
         <v>310</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>33</v>
@@ -8127,7 +8121,7 @@
         <v>312</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -8173,7 +8167,7 @@
         <v>317</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -8184,7 +8178,7 @@
         <v>319</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>320</v>
@@ -8219,7 +8213,7 @@
         <v>321</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -8265,7 +8259,7 @@
         <v>326</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -8311,7 +8305,7 @@
         <v>331</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -8322,7 +8316,7 @@
         <v>333</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>334</v>
@@ -8357,7 +8351,7 @@
         <v>336</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -8368,10 +8362,10 @@
         <v>338</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>33</v>
@@ -8394,7 +8388,7 @@
         <v>340</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -8437,7 +8431,7 @@
         <v>345</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -8448,7 +8442,7 @@
         <v>347</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>348</v>
@@ -8483,11 +8477,11 @@
         <v>350</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>351</v>
@@ -8496,7 +8490,7 @@
         <v>352</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>353</v>
@@ -8531,7 +8525,7 @@
         <v>355</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -8577,11 +8571,11 @@
         <v>360</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>361</v>
@@ -8602,7 +8596,7 @@
         <v>75</v>
       </c>
       <c r="K74" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="L74">
         <v>3662</v>
@@ -8622,11 +8616,11 @@
         <v>364</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>365</v>
@@ -8638,7 +8632,7 @@
         <v>366</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>21</v>
@@ -8664,14 +8658,14 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>368</v>
@@ -8715,7 +8709,7 @@
         <v>373</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -8763,7 +8757,7 @@
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>379</v>
@@ -8809,7 +8803,7 @@
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>384</v>
@@ -8818,7 +8812,7 @@
         <v>385</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>386</v>
@@ -8859,7 +8853,7 @@
         <v>390</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>391</v>
@@ -8871,7 +8865,7 @@
         <v>41</v>
       </c>
       <c r="K80" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="L80">
         <v>279500</v>
@@ -8888,14 +8882,14 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>393</v>
@@ -8904,7 +8898,7 @@
         <v>394</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>395</v>
@@ -8939,7 +8933,7 @@
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>397</v>
@@ -8948,7 +8942,7 @@
         <v>398</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>399</v>
@@ -8980,24 +8974,24 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>1049</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>1050</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>398</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>33</v>
@@ -9006,7 +9000,7 @@
         <v>141</v>
       </c>
       <c r="K83" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="L83">
         <v>2442712</v>
@@ -9073,7 +9067,7 @@
         <v>406</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -9084,7 +9078,7 @@
         <v>408</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>409</v>
@@ -9119,7 +9113,7 @@
         <v>411</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -9186,7 +9180,7 @@
         <v>27</v>
       </c>
       <c r="K87" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="L87">
         <v>38196</v>
@@ -9208,7 +9202,7 @@
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>420</v>
@@ -9229,7 +9223,7 @@
         <v>27</v>
       </c>
       <c r="K88" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="L88">
         <v>10372335</v>
@@ -9293,7 +9287,7 @@
         <v>430</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>431</v>
@@ -9349,7 +9343,7 @@
         <v>59</v>
       </c>
       <c r="K91" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="L91">
         <v>378561</v>
@@ -9381,7 +9375,7 @@
         <v>338</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>40</v>
@@ -9404,7 +9398,7 @@
         <v>442</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -9450,7 +9444,7 @@
         <v>447</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -9461,10 +9455,10 @@
         <v>449</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>21</v>
@@ -9473,7 +9467,7 @@
         <v>22</v>
       </c>
       <c r="K94" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="L94">
         <v>64781</v>
@@ -9493,11 +9487,11 @@
         <v>450</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>451</v>
@@ -9506,7 +9500,7 @@
         <v>452</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>453</v>
@@ -9541,7 +9535,7 @@
         <v>455</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -9552,7 +9546,7 @@
         <v>457</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>458</v>
@@ -9587,7 +9581,7 @@
         <v>460</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -9633,7 +9627,7 @@
         <v>465</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -9644,7 +9638,7 @@
         <v>467</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>468</v>
@@ -9721,26 +9715,26 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="E100" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="G100" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H100" s="1" t="s">
         <v>1143</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>1419</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>1144</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>21</v>
@@ -9749,7 +9743,7 @@
         <v>27</v>
       </c>
       <c r="K100" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="L100">
         <v>882</v>
@@ -9769,7 +9763,7 @@
         <v>473</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
@@ -9780,7 +9774,7 @@
         <v>475</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>476</v>
@@ -9816,7 +9810,7 @@
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D102" s="1"/>
       <c r="E102" s="1" t="s">
@@ -9838,7 +9832,7 @@
         <v>243</v>
       </c>
       <c r="K102" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="L102">
         <v>7510800</v>
@@ -9896,10 +9890,10 @@
         <v>488</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>21</v>
@@ -9908,7 +9902,7 @@
         <v>22</v>
       </c>
       <c r="K104" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="L104">
         <v>395050</v>
@@ -9931,7 +9925,7 @@
         <v>489</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
@@ -9977,7 +9971,7 @@
         <v>494</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
@@ -10023,7 +10017,7 @@
         <v>499</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
@@ -10060,7 +10054,7 @@
         <v>504</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
@@ -10071,7 +10065,7 @@
         <v>506</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>507</v>
@@ -10106,7 +10100,7 @@
         <v>509</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
@@ -10117,7 +10111,7 @@
         <v>511</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>512</v>
@@ -10149,12 +10143,12 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>651</v>
@@ -10175,7 +10169,7 @@
         <v>22</v>
       </c>
       <c r="K110" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="L110">
         <v>84523</v>
@@ -10189,7 +10183,7 @@
         <v>514</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
@@ -10237,7 +10231,7 @@
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="D112" s="1" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>520</v>
@@ -10281,11 +10275,11 @@
         <v>524</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>525</v>
@@ -10294,7 +10288,7 @@
         <v>526</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>527</v>
@@ -10382,7 +10376,7 @@
         <v>536</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>537</v>
@@ -10417,7 +10411,7 @@
         <v>539</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
@@ -10440,7 +10434,7 @@
         <v>22</v>
       </c>
       <c r="K116" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="L116">
         <v>103267</v>
@@ -10460,7 +10454,7 @@
         <v>543</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
@@ -10506,7 +10500,7 @@
         <v>548</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
@@ -10543,7 +10537,7 @@
         <v>554</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
@@ -10589,7 +10583,7 @@
         <v>559</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
@@ -10600,7 +10594,7 @@
         <v>561</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>562</v>
@@ -10635,7 +10629,7 @@
         <v>564</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
@@ -10646,7 +10640,7 @@
         <v>566</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>567</v>
@@ -10672,7 +10666,7 @@
         <v>569</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
@@ -10683,7 +10677,7 @@
         <v>571</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>572</v>
@@ -10720,7 +10714,7 @@
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>575</v>
@@ -10757,7 +10751,7 @@
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="D124" s="1" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>580</v>
@@ -10792,7 +10786,7 @@
         <v>584</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
@@ -10803,7 +10797,7 @@
         <v>586</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>587</v>
@@ -10840,7 +10834,7 @@
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>590</v>
@@ -10849,7 +10843,7 @@
         <v>591</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>592</v>
@@ -10881,7 +10875,7 @@
         <v>594</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
@@ -10904,7 +10898,7 @@
         <v>168</v>
       </c>
       <c r="K127" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="L127">
         <v>2116427</v>
@@ -10927,7 +10921,7 @@
         <v>598</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
@@ -10973,7 +10967,7 @@
         <v>603</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
@@ -10987,7 +10981,7 @@
         <v>605</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>33</v>
@@ -11019,7 +11013,7 @@
         <v>607</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
@@ -11042,7 +11036,7 @@
         <v>98</v>
       </c>
       <c r="K130" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="L130">
         <v>41237</v>
@@ -11062,7 +11056,7 @@
         <v>611</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
@@ -11073,7 +11067,7 @@
         <v>613</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>614</v>
@@ -11108,7 +11102,7 @@
         <v>616</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
@@ -11131,7 +11125,7 @@
         <v>98</v>
       </c>
       <c r="K132" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="L132">
         <v>690959</v>
@@ -11142,7 +11136,7 @@
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -11159,7 +11153,7 @@
         <v>692</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>15</v>
@@ -11168,7 +11162,7 @@
         <v>243</v>
       </c>
       <c r="K133" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="L133">
         <v>688100</v>
@@ -11182,7 +11176,7 @@
         <v>622</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
@@ -11228,7 +11222,7 @@
         <v>627</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
@@ -11239,7 +11233,7 @@
         <v>629</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>630</v>
@@ -11318,11 +11312,11 @@
         <v>637</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>638</v>
@@ -11334,7 +11328,7 @@
         <v>639</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>15</v>
@@ -11366,7 +11360,7 @@
         <v>641</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
@@ -11403,7 +11397,7 @@
         <v>646</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
@@ -11449,7 +11443,7 @@
         <v>654</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
@@ -11460,7 +11454,7 @@
         <v>656</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>657</v>
@@ -11504,7 +11498,7 @@
         <v>661</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>662</v>
@@ -11516,7 +11510,7 @@
         <v>59</v>
       </c>
       <c r="K141" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="L141">
         <v>349925</v>
@@ -11530,7 +11524,7 @@
         <v>663</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
@@ -11576,7 +11570,7 @@
         <v>668</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
@@ -11622,7 +11616,7 @@
         <v>673</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
@@ -11667,7 +11661,7 @@
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
       <c r="D145" s="1" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>679</v>
@@ -11679,7 +11673,7 @@
         <v>680</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>58</v>
@@ -11711,7 +11705,7 @@
         <v>440</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
@@ -11757,7 +11751,7 @@
         <v>686</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
@@ -11771,7 +11765,7 @@
         <v>688</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>21</v>
@@ -11803,7 +11797,7 @@
         <v>690</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
@@ -11826,7 +11820,7 @@
         <v>98</v>
       </c>
       <c r="K148" s="2" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="L148">
         <v>38857</v>
@@ -11852,7 +11846,7 @@
         <v>624</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>15</v>
@@ -11893,7 +11887,7 @@
         <v>699</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>700</v>
@@ -11969,7 +11963,7 @@
         <v>707</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
@@ -12015,7 +12009,7 @@
         <v>712</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
@@ -12061,11 +12055,11 @@
         <v>717</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C154" s="1"/>
       <c r="D154" s="1" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>718</v>
@@ -12077,7 +12071,7 @@
         <v>145</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>15</v>
@@ -12109,7 +12103,7 @@
         <v>721</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
@@ -12120,7 +12114,7 @@
         <v>723</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>724</v>
@@ -12155,7 +12149,7 @@
         <v>726</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
@@ -12201,7 +12195,7 @@
         <v>731</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
@@ -12238,7 +12232,7 @@
         <v>736</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
@@ -12287,7 +12281,7 @@
         <v>743</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>40</v>
@@ -12337,7 +12331,7 @@
         <v>92</v>
       </c>
       <c r="K160" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="L160">
         <v>5361300</v>
@@ -12351,7 +12345,7 @@
         <v>749</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
@@ -12397,7 +12391,7 @@
         <v>754</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
@@ -12443,7 +12437,7 @@
         <v>759</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
@@ -12530,7 +12524,7 @@
         <v>769</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
@@ -12575,7 +12569,7 @@
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
       <c r="D166" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>773</v>
@@ -12616,7 +12610,7 @@
         <v>777</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
@@ -12662,7 +12656,7 @@
         <v>782</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
@@ -12673,7 +12667,7 @@
         <v>784</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="H168" s="1" t="s">
         <v>785</v>
@@ -12685,7 +12679,7 @@
         <v>440</v>
       </c>
       <c r="K168" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="L168">
         <v>47329</v>
@@ -12705,7 +12699,7 @@
         <v>786</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
@@ -12751,7 +12745,7 @@
         <v>791</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
@@ -12797,7 +12791,7 @@
         <v>796</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
@@ -12840,7 +12834,7 @@
         <v>801</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
@@ -12854,7 +12848,7 @@
         <v>806</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>40</v>
@@ -12883,14 +12877,14 @@
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C173" s="1"/>
       <c r="D173" s="1" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>805</v>
@@ -12932,7 +12926,7 @@
         <v>809</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
@@ -12978,7 +12972,7 @@
         <v>814</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
@@ -12989,7 +12983,7 @@
         <v>816</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="H175" s="1" t="s">
         <v>817</v>
@@ -13015,7 +13009,7 @@
         <v>819</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
@@ -13061,7 +13055,7 @@
         <v>824</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
@@ -13107,11 +13101,11 @@
         <v>829</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C178" s="1"/>
       <c r="D178" s="1" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>830</v>
@@ -13120,7 +13114,7 @@
         <v>831</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="H178" s="1" t="s">
         <v>832</v>
@@ -13143,16 +13137,16 @@
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C179" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>1205</v>
-      </c>
       <c r="D179" s="1" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>834</v>
@@ -13161,7 +13155,7 @@
         <v>835</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="H179" s="1" t="s">
         <v>836</v>
@@ -13173,7 +13167,7 @@
         <v>41</v>
       </c>
       <c r="K179" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="L179">
         <v>35</v>
@@ -13193,7 +13187,7 @@
         <v>837</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
@@ -13241,7 +13235,7 @@
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
       <c r="D181" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>843</v>
@@ -13250,7 +13244,7 @@
         <v>844</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>845</v>
@@ -13285,7 +13279,7 @@
         <v>847</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
@@ -13296,7 +13290,7 @@
         <v>849</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="H182" s="1" t="s">
         <v>850</v>
@@ -13331,7 +13325,7 @@
         <v>852</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
@@ -13374,7 +13368,7 @@
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -13398,7 +13392,7 @@
         <v>180</v>
       </c>
       <c r="K184" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="L184">
         <v>910985</v>
@@ -13458,7 +13452,7 @@
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>866</v>
@@ -13502,7 +13496,7 @@
         <v>870</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
@@ -13545,7 +13539,7 @@
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -13594,7 +13588,7 @@
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
       <c r="D189" s="1" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>880</v>
@@ -13679,13 +13673,13 @@
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C191" s="1" t="s">
         <v>1201</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>1202</v>
       </c>
       <c r="D191" s="1"/>
       <c r="E191" s="1" t="s">
@@ -13695,7 +13689,7 @@
         <v>902</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="H191" s="1" t="s">
         <v>903</v>
@@ -13727,7 +13721,7 @@
         <v>889</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
@@ -13738,7 +13732,7 @@
         <v>891</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H192" s="1" t="s">
         <v>892</v>
@@ -13772,7 +13766,7 @@
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>895</v>
@@ -13793,7 +13787,7 @@
         <v>59</v>
       </c>
       <c r="K193" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="L193">
         <v>109296</v>
@@ -13804,14 +13798,14 @@
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="C194" s="1"/>
       <c r="D194" s="1" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>898</v>
@@ -13820,7 +13814,7 @@
         <v>899</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="H194" s="1" t="s">
         <v>900</v>
@@ -13832,7 +13826,7 @@
         <v>59</v>
       </c>
       <c r="K194" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="L194">
         <v>10562</v>
@@ -13852,7 +13846,7 @@
         <v>905</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
@@ -13898,7 +13892,7 @@
         <v>910</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
@@ -13912,7 +13906,7 @@
         <v>912</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>1236</v>
+        <v>910</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>21</v>
@@ -13941,10 +13935,10 @@
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
@@ -13955,10 +13949,10 @@
         <v>915</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>33</v>
@@ -13967,7 +13961,7 @@
         <v>52</v>
       </c>
       <c r="K197" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="L197">
         <v>209607</v>
@@ -13990,7 +13984,7 @@
         <v>916</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
@@ -14027,7 +14021,7 @@
         <v>921</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
@@ -14073,7 +14067,7 @@
         <v>926</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
@@ -14084,7 +14078,7 @@
         <v>928</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="H200" s="1" t="s">
         <v>929</v>
@@ -14119,7 +14113,7 @@
         <v>931</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
@@ -14130,7 +14124,7 @@
         <v>933</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H201" s="1" t="s">
         <v>934</v>
@@ -14165,7 +14159,7 @@
         <v>936</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
@@ -14211,7 +14205,7 @@
         <v>941</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
@@ -14225,7 +14219,7 @@
         <v>923</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>15</v>
@@ -14234,7 +14228,7 @@
         <v>185</v>
       </c>
       <c r="K203" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="L203">
         <v>6110200</v>
@@ -14254,24 +14248,24 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B204" s="1"/>
       <c r="C204" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D204" s="1"/>
       <c r="E204" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="F204" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="F204" s="1" t="s">
+      <c r="G204" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="H204" s="1" t="s">
         <v>947</v>
-      </c>
-      <c r="G204" s="1" t="s">
-        <v>1433</v>
-      </c>
-      <c r="H204" s="1" t="s">
-        <v>948</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>58</v>
@@ -14280,7 +14274,7 @@
         <v>59</v>
       </c>
       <c r="K204" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="L204">
         <v>41349</v>
@@ -14297,24 +14291,24 @@
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="E205" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="F205" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="F205" s="1" t="s">
+      <c r="G205" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="H205" s="1" t="s">
         <v>952</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>1453</v>
-      </c>
-      <c r="H205" s="1" t="s">
-        <v>953</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>21</v>
@@ -14323,7 +14317,7 @@
         <v>124</v>
       </c>
       <c r="K205" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="L205">
         <v>5405368</v>
@@ -14343,24 +14337,24 @@
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F206" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="F206" s="1" t="s">
+      <c r="G206" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="H206" s="1" t="s">
         <v>957</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>957</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>958</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>21</v>
@@ -14369,7 +14363,7 @@
         <v>27</v>
       </c>
       <c r="K206" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="L206">
         <v>2135107</v>
@@ -14380,26 +14374,26 @@
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C207" s="1"/>
       <c r="D207" s="1" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="E207" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F207" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="F207" s="1" t="s">
+      <c r="G207" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H207" s="1" t="s">
         <v>962</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>1452</v>
-      </c>
-      <c r="H207" s="1" t="s">
-        <v>963</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>40</v>
@@ -14408,7 +14402,7 @@
         <v>371</v>
       </c>
       <c r="K207" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="L207">
         <v>750325</v>
@@ -14428,24 +14422,24 @@
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="F208" s="1" t="s">
+      <c r="G208" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="H208" s="1" t="s">
         <v>966</v>
-      </c>
-      <c r="G208" s="1" t="s">
-        <v>966</v>
-      </c>
-      <c r="H208" s="1" t="s">
-        <v>967</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>33</v>
@@ -14454,7 +14448,7 @@
         <v>180</v>
       </c>
       <c r="K208" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L208">
         <v>19655000</v>
@@ -14465,24 +14459,24 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="F209" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="F209" s="1" t="s">
+      <c r="G209" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H209" s="1" t="s">
         <v>971</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>1435</v>
-      </c>
-      <c r="H209" s="1" t="s">
-        <v>972</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>33</v>
@@ -14491,7 +14485,7 @@
         <v>168</v>
       </c>
       <c r="K209" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="L209">
         <v>63100945</v>
@@ -14511,26 +14505,26 @@
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C210" s="1"/>
       <c r="D210" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="E210" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="E210" s="1" t="s">
+      <c r="F210" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="F210" s="1" t="s">
-        <v>976</v>
-      </c>
       <c r="G210" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>58</v>
@@ -14539,7 +14533,7 @@
         <v>75</v>
       </c>
       <c r="K210" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="L210">
         <v>20</v>
@@ -14556,24 +14550,24 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E211" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="F211" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="F211" s="1" t="s">
+      <c r="G211" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="H211" s="1" t="s">
         <v>979</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>1451</v>
-      </c>
-      <c r="H211" s="1" t="s">
-        <v>980</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>15</v>
@@ -14582,7 +14576,7 @@
         <v>243</v>
       </c>
       <c r="K211" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="L211">
         <v>51097986</v>
@@ -14602,24 +14596,24 @@
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="F212" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="F212" s="1" t="s">
+      <c r="G212" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H212" s="1" t="s">
         <v>984</v>
-      </c>
-      <c r="G212" s="1" t="s">
-        <v>1450</v>
-      </c>
-      <c r="H212" s="1" t="s">
-        <v>985</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>33</v>
@@ -14628,7 +14622,7 @@
         <v>52</v>
       </c>
       <c r="K212" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="L212">
         <v>15786898</v>
@@ -14648,24 +14642,24 @@
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="F213" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="F213" s="1" t="s">
+      <c r="G213" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="H213" s="1" t="s">
         <v>989</v>
-      </c>
-      <c r="G213" s="1" t="s">
-        <v>1434</v>
-      </c>
-      <c r="H213" s="1" t="s">
-        <v>990</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>21</v>
@@ -14674,7 +14668,7 @@
         <v>27</v>
       </c>
       <c r="K213" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="L213">
         <v>49687120</v>
@@ -14694,24 +14688,24 @@
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="F214" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="F214" s="1" t="s">
+      <c r="G214" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H214" s="1" t="s">
         <v>994</v>
-      </c>
-      <c r="G214" s="1" t="s">
-        <v>1386</v>
-      </c>
-      <c r="H214" s="1" t="s">
-        <v>995</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>15</v>
@@ -14720,7 +14714,7 @@
         <v>16</v>
       </c>
       <c r="K214" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="L214">
         <v>21781800</v>
@@ -14737,24 +14731,24 @@
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="F215" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="F215" s="1" t="s">
+      <c r="G215" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H215" s="1" t="s">
         <v>999</v>
-      </c>
-      <c r="G215" s="1" t="s">
-        <v>1436</v>
-      </c>
-      <c r="H215" s="1" t="s">
-        <v>1000</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>33</v>
@@ -14763,7 +14757,7 @@
         <v>34</v>
       </c>
       <c r="K215" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="L215">
         <v>51662000</v>
@@ -14783,24 +14777,24 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F216" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="F216" s="1" t="s">
+      <c r="G216" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H216" s="1" t="s">
         <v>1004</v>
-      </c>
-      <c r="G216" s="1" t="s">
-        <v>1457</v>
-      </c>
-      <c r="H216" s="1" t="s">
-        <v>1005</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>58</v>
@@ -14809,7 +14803,7 @@
         <v>75</v>
       </c>
       <c r="K216" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="L216">
         <v>616500</v>
@@ -14829,26 +14823,26 @@
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D217" s="1"/>
       <c r="E217" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F217" s="1" t="s">
         <v>1007</v>
-      </c>
-      <c r="F217" s="1" t="s">
-        <v>1008</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>333</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>21</v>
@@ -14857,7 +14851,7 @@
         <v>22</v>
       </c>
       <c r="K217" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="L217">
         <f>2881</f>
@@ -14875,24 +14869,24 @@
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F218" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="F218" s="1" t="s">
+      <c r="G218" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H218" s="1" t="s">
         <v>1013</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>1437</v>
-      </c>
-      <c r="H218" s="1" t="s">
-        <v>1014</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>21</v>
@@ -14901,7 +14895,7 @@
         <v>22</v>
       </c>
       <c r="K218" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="L218">
         <v>10608128</v>
@@ -14921,24 +14915,24 @@
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
       <c r="D219" s="1" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="E219" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>1017</v>
-      </c>
-      <c r="F219" s="1" t="s">
-        <v>1018</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>352</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>21</v>
@@ -14947,7 +14941,7 @@
         <v>98</v>
       </c>
       <c r="K219" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L219">
         <v>9139676</v>
@@ -14967,24 +14961,24 @@
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="E220" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F220" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="F220" s="1" t="s">
+      <c r="G220" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H220" s="1" t="s">
         <v>1023</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="H220" s="1" t="s">
-        <v>1024</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>15</v>
@@ -14993,7 +14987,7 @@
         <v>81</v>
       </c>
       <c r="K220" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="L220">
         <v>26472497</v>
@@ -15010,26 +15004,26 @@
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B221" s="1"/>
       <c r="C221" s="1" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="E221" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F221" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="F221" s="1" t="s">
+      <c r="G221" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H221" s="1" t="s">
         <v>1028</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="H221" s="1" t="s">
-        <v>1029</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>15</v>
@@ -15038,7 +15032,7 @@
         <v>243</v>
       </c>
       <c r="K221" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="L221">
         <v>23243565</v>
@@ -15049,24 +15043,24 @@
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F222" s="1" t="s">
         <v>1031</v>
       </c>
-      <c r="F222" s="1" t="s">
+      <c r="G222" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H222" s="1" t="s">
         <v>1032</v>
-      </c>
-      <c r="G222" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="H222" s="1" t="s">
-        <v>1033</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>15</v>
@@ -15075,7 +15069,7 @@
         <v>552</v>
       </c>
       <c r="K222" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="L222">
         <v>10721000</v>
@@ -15095,24 +15089,24 @@
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F223" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="F223" s="1" t="s">
+      <c r="G223" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H223" s="1" t="s">
         <v>1037</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>1037</v>
-      </c>
-      <c r="H223" s="1" t="s">
-        <v>1038</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>33</v>
@@ -15121,7 +15115,7 @@
         <v>180</v>
       </c>
       <c r="K223" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="L223">
         <v>68153004</v>
@@ -15141,24 +15135,24 @@
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F224" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="F224" s="1" t="s">
+      <c r="G224" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H224" s="1" t="s">
         <v>1042</v>
-      </c>
-      <c r="G224" s="1" t="s">
-        <v>1042</v>
-      </c>
-      <c r="H224" s="1" t="s">
-        <v>1043</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>15</v>
@@ -15167,7 +15161,7 @@
         <v>185</v>
       </c>
       <c r="K224" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="L224">
         <v>65706765</v>
@@ -15187,26 +15181,26 @@
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C225" s="1"/>
       <c r="D225" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E225" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F225" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="F225" s="1" t="s">
+      <c r="G225" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H225" s="1" t="s">
         <v>1055</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="H225" s="1" t="s">
-        <v>1056</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>15</v>
@@ -15215,7 +15209,7 @@
         <v>185</v>
       </c>
       <c r="K225" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="L225">
         <v>1391221</v>
@@ -15235,24 +15229,24 @@
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
       <c r="D226" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E226" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F226" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="F226" s="1" t="s">
-        <v>1060</v>
-      </c>
       <c r="G226" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>33</v>
@@ -15261,7 +15255,7 @@
         <v>141</v>
       </c>
       <c r="K226" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="L226">
         <v>8095498</v>
@@ -15281,23 +15275,23 @@
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D227" s="1"/>
       <c r="E227" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F227" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="F227" s="1" t="s">
-        <v>1064</v>
-      </c>
       <c r="G227" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H227" s="1" t="e">
         <f>NA()</f>
@@ -15310,7 +15304,7 @@
         <v>41</v>
       </c>
       <c r="K227" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="L227">
         <v>2691</v>
@@ -15327,24 +15321,24 @@
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F228" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="F228" s="1" t="s">
+      <c r="G228" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H228" s="1" t="s">
         <v>1068</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>1078</v>
-      </c>
-      <c r="H228" s="1" t="s">
-        <v>1069</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>40</v>
@@ -15353,7 +15347,7 @@
         <v>41</v>
       </c>
       <c r="K228" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="L228">
         <v>100179</v>
@@ -15373,24 +15367,24 @@
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F229" s="1" t="s">
         <v>1072</v>
-      </c>
-      <c r="F229" s="1" t="s">
-        <v>1073</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>231</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>58</v>
@@ -15399,7 +15393,7 @@
         <v>59</v>
       </c>
       <c r="K229" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L229">
         <v>1367764</v>
@@ -15419,24 +15413,24 @@
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F230" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="F230" s="1" t="s">
+      <c r="G230" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H230" s="1" t="s">
         <v>1078</v>
-      </c>
-      <c r="G230" s="1" t="s">
-        <v>1439</v>
-      </c>
-      <c r="H230" s="1" t="s">
-        <v>1079</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>33</v>
@@ -15445,7 +15439,7 @@
         <v>34</v>
       </c>
       <c r="K230" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="L230">
         <v>11972169</v>
@@ -15465,26 +15459,26 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C231" s="1"/>
       <c r="D231" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E231" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="E231" s="1" t="s">
+      <c r="F231" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="F231" s="1" t="s">
+      <c r="G231" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="H231" s="1" t="s">
         <v>1083</v>
-      </c>
-      <c r="G231" s="1" t="s">
-        <v>1440</v>
-      </c>
-      <c r="H231" s="1" t="s">
-        <v>1084</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>15</v>
@@ -15493,7 +15487,7 @@
         <v>81</v>
       </c>
       <c r="K231" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="L231">
         <v>86092168</v>
@@ -15513,22 +15507,22 @@
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F232" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="F232" s="1" t="s">
+      <c r="G232" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H232" s="1" t="s">
         <v>1088</v>
-      </c>
-      <c r="G232" s="1" t="s">
-        <v>1441</v>
-      </c>
-      <c r="H232" s="1" t="s">
-        <v>1089</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>15</v>
@@ -15537,7 +15531,7 @@
         <v>552</v>
       </c>
       <c r="K232" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="L232">
         <v>7057841</v>
@@ -15557,24 +15551,24 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F233" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="F233" s="1" t="s">
+      <c r="G233" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H233" s="1" t="s">
         <v>1093</v>
-      </c>
-      <c r="G233" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="H233" s="1" t="s">
-        <v>1094</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>58</v>
@@ -15583,7 +15577,7 @@
         <v>59</v>
       </c>
       <c r="K233" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="L233">
         <v>50828</v>
@@ -15600,22 +15594,22 @@
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F234" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="F234" s="1" t="s">
+      <c r="G234" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H234" s="1" t="s">
         <v>1097</v>
-      </c>
-      <c r="G234" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="H234" s="1" t="s">
-        <v>1098</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>40</v>
@@ -15624,7 +15618,7 @@
         <v>41</v>
       </c>
       <c r="K234" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="L234">
         <v>10643</v>
@@ -15644,24 +15638,24 @@
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F235" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="F235" s="1" t="s">
+      <c r="G235" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H235" s="1" t="s">
         <v>1102</v>
-      </c>
-      <c r="G235" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="H235" s="1" t="s">
-        <v>1103</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>33</v>
@@ -15670,7 +15664,7 @@
         <v>180</v>
       </c>
       <c r="K235" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="L235">
         <v>45905417</v>
@@ -15690,22 +15684,22 @@
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F236" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="F236" s="1" t="s">
+      <c r="G236" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="H236" s="1" t="s">
         <v>1107</v>
-      </c>
-      <c r="G236" s="1" t="s">
-        <v>1442</v>
-      </c>
-      <c r="H236" s="1" t="s">
-        <v>1108</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>21</v>
@@ -15714,7 +15708,7 @@
         <v>124</v>
       </c>
       <c r="K236" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="L236">
         <v>28700000</v>
@@ -15734,26 +15728,26 @@
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C237" s="1"/>
       <c r="D237" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E237" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F237" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="F237" s="1" t="s">
+      <c r="G237" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H237" s="1" t="s">
         <v>1112</v>
-      </c>
-      <c r="G237" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="H237" s="1" t="s">
-        <v>1113</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>15</v>
@@ -15762,7 +15756,7 @@
         <v>81</v>
       </c>
       <c r="K237" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="L237">
         <v>11294243</v>
@@ -15773,28 +15767,28 @@
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E238" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>1326</v>
-      </c>
-      <c r="D238" s="1" t="s">
-        <v>1327</v>
-      </c>
-      <c r="E238" s="1" t="s">
+      <c r="F238" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="F238" s="1" t="s">
+      <c r="G238" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H238" s="1" t="s">
         <v>1117</v>
-      </c>
-      <c r="G238" s="1" t="s">
-        <v>1449</v>
-      </c>
-      <c r="H238" s="1" t="s">
-        <v>1118</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>21</v>
@@ -15803,7 +15797,7 @@
         <v>22</v>
       </c>
       <c r="K238" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="L238">
         <v>69487000</v>
@@ -15814,28 +15808,28 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D239" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D239" s="1" t="s">
+      <c r="E239" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F239" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="E239" s="1" t="s">
+      <c r="G239" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="F239" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>1122</v>
-      </c>
       <c r="H239" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>58</v>
@@ -15844,7 +15838,7 @@
         <v>147</v>
       </c>
       <c r="K239" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L239">
         <v>341784857</v>
@@ -15864,21 +15858,21 @@
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F240" s="1" t="s">
         <v>1125</v>
       </c>
-      <c r="F240" s="1" t="s">
-        <v>1126</v>
-      </c>
       <c r="G240" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H240" s="1" t="e">
         <f>NA()</f>
@@ -15891,7 +15885,7 @@
         <v>147</v>
       </c>
       <c r="K240" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L240">
         <v>300</v>
@@ -15908,26 +15902,26 @@
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C241" s="1"/>
       <c r="D241" s="1" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="E241" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F241" s="1" t="s">
         <v>1159</v>
       </c>
-      <c r="F241" s="1" t="s">
+      <c r="G241" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H241" s="1" t="s">
         <v>1160</v>
-      </c>
-      <c r="G241" s="1" t="s">
-        <v>1443</v>
-      </c>
-      <c r="H241" s="1" t="s">
-        <v>1161</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>58</v>
@@ -15936,7 +15930,7 @@
         <v>59</v>
       </c>
       <c r="K241" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="L241">
         <v>87146</v>
@@ -15953,24 +15947,24 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F242" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="F242" s="1" t="s">
+      <c r="G242" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H242" s="1" t="s">
         <v>1129</v>
-      </c>
-      <c r="G242" s="1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="H242" s="1" t="s">
-        <v>1130</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>58</v>
@@ -15979,7 +15973,7 @@
         <v>75</v>
       </c>
       <c r="K242" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L242">
         <v>3485931</v>
@@ -15999,24 +15993,24 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F243" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="F243" s="1" t="s">
+      <c r="G243" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H243" s="1" t="s">
         <v>1134</v>
-      </c>
-      <c r="G243" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="H243" s="1" t="s">
-        <v>1135</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>15</v>
@@ -16025,7 +16019,7 @@
         <v>552</v>
       </c>
       <c r="K243" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L243">
         <v>39047321</v>
@@ -16036,24 +16030,24 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F244" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="F244" s="1" t="s">
+      <c r="G244" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="H244" s="1" t="s">
         <v>1139</v>
-      </c>
-      <c r="G244" s="1" t="s">
-        <v>1448</v>
-      </c>
-      <c r="H244" s="1" t="s">
-        <v>1140</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>40</v>
@@ -16062,7 +16056,7 @@
         <v>371</v>
       </c>
       <c r="K244" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="L244">
         <v>321409</v>
@@ -16073,24 +16067,24 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F245" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="F245" s="1" t="s">
+      <c r="G245" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H245" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="G245" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="H245" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>58</v>
@@ -16099,7 +16093,7 @@
         <v>75</v>
       </c>
       <c r="K245" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="L245">
         <v>28517000</v>
@@ -16119,24 +16113,24 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
       <c r="D246" s="1" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="E246" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F246" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="F246" s="1" t="s">
+      <c r="G246" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="H246" s="1" t="s">
         <v>1153</v>
-      </c>
-      <c r="G246" s="1" t="s">
-        <v>1444</v>
-      </c>
-      <c r="H246" s="1" t="s">
-        <v>1154</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>15</v>
@@ -16145,7 +16139,7 @@
         <v>185</v>
       </c>
       <c r="K246" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="L246">
         <v>102300000</v>
@@ -16165,28 +16159,28 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="E247" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F247" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="F247" s="1" t="s">
+      <c r="G247" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H247" s="1" t="s">
         <v>1163</v>
-      </c>
-      <c r="G247" s="1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="H247" s="1" t="s">
-        <v>1164</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>40</v>
@@ -16195,7 +16189,7 @@
         <v>41</v>
       </c>
       <c r="K247" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="L247">
         <v>11620</v>
@@ -16206,24 +16200,24 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
       <c r="D248" s="1" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="E248" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F248" s="1" t="s">
         <v>1167</v>
       </c>
-      <c r="F248" s="1" t="s">
-        <v>1168</v>
-      </c>
       <c r="G248" s="1" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>33</v>
@@ -16232,7 +16226,7 @@
         <v>34</v>
       </c>
       <c r="K248" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="L248">
         <v>600904</v>
@@ -16243,24 +16237,24 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F249" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="F249" s="1" t="s">
+      <c r="G249" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H249" s="1" t="s">
         <v>1172</v>
-      </c>
-      <c r="G249" s="1" t="s">
-        <v>1446</v>
-      </c>
-      <c r="H249" s="1" t="s">
-        <v>1173</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>15</v>
@@ -16269,7 +16263,7 @@
         <v>81</v>
       </c>
       <c r="K249" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L249">
         <v>32684503</v>
@@ -16289,24 +16283,24 @@
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F250" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="F250" s="1" t="s">
+      <c r="G250" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="H250" s="1" t="s">
         <v>1177</v>
-      </c>
-      <c r="G250" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="H250" s="1" t="s">
-        <v>1178</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>33</v>
@@ -16315,7 +16309,7 @@
         <v>168</v>
       </c>
       <c r="K250" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="L250">
         <v>19693423</v>
@@ -16335,24 +16329,24 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F251" s="1" t="s">
         <v>1181</v>
       </c>
-      <c r="F251" s="1" t="s">
+      <c r="G251" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H251" s="1" t="s">
         <v>1182</v>
-      </c>
-      <c r="G251" s="1" t="s">
-        <v>1447</v>
-      </c>
-      <c r="H251" s="1" t="s">
-        <v>1183</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>33</v>
@@ -16361,7 +16355,7 @@
         <v>180</v>
       </c>
       <c r="K251" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L251">
         <v>17073087</v>
